--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1337 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122721910</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>519754</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7035420</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122721724</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>519765</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7035442</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122721914</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>519756</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7035416</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122722054</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7035414</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122722231</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519782</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7035501</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122721713</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519772</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7035431</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122722127</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519724</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7035446</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122721503</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519795</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7035472</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122722060</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79770</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>519759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7035412</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122721845</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>519759</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7035436</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122721604</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djupmyren, Djupmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>519781</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7035475</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721914</v>
+        <v>122721713</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519756</v>
+        <v>519772</v>
       </c>
       <c r="R3" t="n">
-        <v>7035416</v>
+        <v>7035431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721713</v>
+        <v>122721503</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,14 +965,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519772</v>
+        <v>519795</v>
       </c>
       <c r="R4" t="n">
-        <v>7035431</v>
+        <v>7035472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +1009,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,31 +1020,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721503</v>
+        <v>122721604</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1052,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519795</v>
+        <v>519781</v>
       </c>
       <c r="R5" t="n">
-        <v>7035472</v>
+        <v>7035475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,11 +1114,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,6 +1122,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122722060</v>
+        <v>122722054</v>
       </c>
       <c r="B6" t="n">
-        <v>79872</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,31 +1175,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519759</v>
+        <v>519758</v>
       </c>
       <c r="R6" t="n">
-        <v>7035412</v>
+        <v>7035414</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,6 +1244,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721604</v>
+        <v>122721914</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,34 +1316,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519781</v>
+        <v>519756</v>
       </c>
       <c r="R7" t="n">
-        <v>7035475</v>
+        <v>7035416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,31 +1391,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1402,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122722054</v>
+        <v>122721724</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,39 +1423,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519758</v>
+        <v>519765</v>
       </c>
       <c r="R8" t="n">
-        <v>7035414</v>
+        <v>7035442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,31 +1503,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1539,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122722231</v>
+        <v>122722127</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,48 +1535,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519782</v>
+        <v>519724</v>
       </c>
       <c r="R9" t="n">
-        <v>7035501</v>
+        <v>7035446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,6 +1605,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1655,7 +1646,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721724</v>
+        <v>122721845</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1700,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519765</v>
+        <v>519759</v>
       </c>
       <c r="R10" t="n">
-        <v>7035442</v>
+        <v>7035436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,7 +1731,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722127</v>
+        <v>122722231</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,34 +1774,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519724</v>
+        <v>519782</v>
       </c>
       <c r="R11" t="n">
-        <v>7035446</v>
+        <v>7035501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,31 +1858,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,10 +1874,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721910</v>
+        <v>122722060</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,31 +1886,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1939,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519754</v>
+        <v>519759</v>
       </c>
       <c r="R12" t="n">
-        <v>7035420</v>
+        <v>7035412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,11 +1957,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1990,6 +1965,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2006,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721845</v>
+        <v>122721910</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519759</v>
+        <v>519754</v>
       </c>
       <c r="R13" t="n">
-        <v>7035436</v>
+        <v>7035420</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721713</v>
+        <v>122721910</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519772</v>
+        <v>519754</v>
       </c>
       <c r="R3" t="n">
-        <v>7035431</v>
+        <v>7035420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721503</v>
+        <v>122721604</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519795</v>
+        <v>519781</v>
       </c>
       <c r="R4" t="n">
-        <v>7035472</v>
+        <v>7035475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,11 +977,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,6 +985,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721604</v>
+        <v>122722060</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1038,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519781</v>
+        <v>519759</v>
       </c>
       <c r="R5" t="n">
-        <v>7035475</v>
+        <v>7035412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,22 +1125,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122722054</v>
+        <v>122721713</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,27 +1174,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519758</v>
+        <v>519772</v>
       </c>
       <c r="R6" t="n">
-        <v>7035414</v>
+        <v>7035431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Äldre ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,22 +1262,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1300,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721914</v>
+        <v>122722054</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,27 +1311,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1345,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519756</v>
+        <v>519758</v>
       </c>
       <c r="R7" t="n">
-        <v>7035416</v>
+        <v>7035414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1391,6 +1391,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1407,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721724</v>
+        <v>122721503</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1443,7 +1468,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1452,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519765</v>
+        <v>519795</v>
       </c>
       <c r="R8" t="n">
-        <v>7035442</v>
+        <v>7035472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122722127</v>
+        <v>122721914</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,34 +1560,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519724</v>
+        <v>519756</v>
       </c>
       <c r="R9" t="n">
-        <v>7035446</v>
+        <v>7035416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,31 +1635,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1646,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721845</v>
+        <v>122721724</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1691,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519759</v>
+        <v>519765</v>
       </c>
       <c r="R10" t="n">
-        <v>7035436</v>
+        <v>7035442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1736,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1874,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722060</v>
+        <v>122722127</v>
       </c>
       <c r="B12" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,43 +1891,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519759</v>
+        <v>519724</v>
       </c>
       <c r="R12" t="n">
-        <v>7035412</v>
+        <v>7035446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1973,22 +1973,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721910</v>
+        <v>122721845</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519754</v>
+        <v>519759</v>
       </c>
       <c r="R13" t="n">
-        <v>7035420</v>
+        <v>7035436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721910</v>
+        <v>122722060</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519754</v>
+        <v>519759</v>
       </c>
       <c r="R3" t="n">
-        <v>7035420</v>
+        <v>7035412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +870,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +878,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721604</v>
+        <v>122721845</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +935,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519781</v>
+        <v>519759</v>
       </c>
       <c r="R4" t="n">
-        <v>7035475</v>
+        <v>7035436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +1002,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,31 +1015,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1026,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722060</v>
+        <v>122721713</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519759</v>
+        <v>519772</v>
       </c>
       <c r="R5" t="n">
-        <v>7035412</v>
+        <v>7035431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,6 +1114,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,22 +1135,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721713</v>
+        <v>122722127</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519772</v>
+        <v>519724</v>
       </c>
       <c r="R6" t="n">
-        <v>7035431</v>
+        <v>7035446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,11 +1246,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722054</v>
+        <v>122722231</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,39 +1311,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519758</v>
+        <v>519782</v>
       </c>
       <c r="R7" t="n">
-        <v>7035414</v>
+        <v>7035501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,11 +1387,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1391,31 +1395,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1432,7 +1411,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721503</v>
+        <v>122721724</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1468,7 +1447,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1477,10 +1456,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519795</v>
+        <v>519765</v>
       </c>
       <c r="R8" t="n">
-        <v>7035472</v>
+        <v>7035442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122721914</v>
+        <v>122722054</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,27 +1539,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1589,10 +1568,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519756</v>
+        <v>519758</v>
       </c>
       <c r="R9" t="n">
-        <v>7035416</v>
+        <v>7035414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,6 +1606,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1635,6 +1619,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1651,7 +1660,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721724</v>
+        <v>122721503</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1687,7 +1696,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1696,10 +1705,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519765</v>
+        <v>519795</v>
       </c>
       <c r="R10" t="n">
-        <v>7035442</v>
+        <v>7035472</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722231</v>
+        <v>122721914</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,48 +1788,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519782</v>
+        <v>519756</v>
       </c>
       <c r="R11" t="n">
-        <v>7035501</v>
+        <v>7035416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722127</v>
+        <v>122721604</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519724</v>
+        <v>519781</v>
       </c>
       <c r="R12" t="n">
-        <v>7035446</v>
+        <v>7035475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721845</v>
+        <v>122721910</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519759</v>
+        <v>519754</v>
       </c>
       <c r="R13" t="n">
-        <v>7035436</v>
+        <v>7035420</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122722127</v>
+        <v>122722231</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,34 +1184,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519724</v>
+        <v>519782</v>
       </c>
       <c r="R6" t="n">
-        <v>7035446</v>
+        <v>7035501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,31 +1268,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722231</v>
+        <v>122722127</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,48 +1300,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519782</v>
+        <v>519724</v>
       </c>
       <c r="R7" t="n">
-        <v>7035501</v>
+        <v>7035446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,6 +1370,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122722060</v>
+        <v>122722054</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519759</v>
+        <v>519758</v>
       </c>
       <c r="R3" t="n">
-        <v>7035412</v>
+        <v>7035414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721845</v>
+        <v>122721604</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519759</v>
+        <v>519781</v>
       </c>
       <c r="R4" t="n">
-        <v>7035436</v>
+        <v>7035475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,11 +1002,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,6 +1010,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721713</v>
+        <v>122722060</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1063,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519772</v>
+        <v>519759</v>
       </c>
       <c r="R5" t="n">
-        <v>7035431</v>
+        <v>7035412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,11 +1134,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1135,22 +1150,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122722231</v>
+        <v>122721713</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,48 +1199,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519782</v>
+        <v>519772</v>
       </c>
       <c r="R6" t="n">
-        <v>7035501</v>
+        <v>7035431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,6 +1266,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,6 +1279,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1284,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722127</v>
+        <v>122721845</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,34 +1336,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519724</v>
+        <v>519759</v>
       </c>
       <c r="R7" t="n">
-        <v>7035446</v>
+        <v>7035436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,6 +1403,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1370,31 +1416,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1411,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721724</v>
+        <v>122721503</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1447,7 +1468,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1456,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519765</v>
+        <v>519795</v>
       </c>
       <c r="R8" t="n">
-        <v>7035442</v>
+        <v>7035472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122722054</v>
+        <v>122721910</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,27 +1560,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1568,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519758</v>
+        <v>519754</v>
       </c>
       <c r="R9" t="n">
-        <v>7035414</v>
+        <v>7035420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1629,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,31 +1640,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1660,7 +1656,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721503</v>
+        <v>122721914</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1701,14 +1697,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519795</v>
+        <v>519756</v>
       </c>
       <c r="R10" t="n">
-        <v>7035472</v>
+        <v>7035416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,11 +1737,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721914</v>
+        <v>122721724</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1808,19 +1799,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519756</v>
+        <v>519765</v>
       </c>
       <c r="R11" t="n">
-        <v>7035416</v>
+        <v>7035442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,6 +1844,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721604</v>
+        <v>122722127</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1919,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519781</v>
+        <v>519724</v>
       </c>
       <c r="R12" t="n">
-        <v>7035475</v>
+        <v>7035446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721910</v>
+        <v>122722231</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,39 +2018,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519754</v>
+        <v>519782</v>
       </c>
       <c r="R13" t="n">
-        <v>7035420</v>
+        <v>7035501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,11 +2092,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122722054</v>
+        <v>122722127</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519758</v>
+        <v>519724</v>
       </c>
       <c r="R3" t="n">
-        <v>7035414</v>
+        <v>7035446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +865,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,22 +881,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721604</v>
+        <v>122721910</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519781</v>
+        <v>519754</v>
       </c>
       <c r="R4" t="n">
-        <v>7035475</v>
+        <v>7035420</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,6 +997,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,31 +1010,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722060</v>
+        <v>122721604</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,43 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519759</v>
+        <v>519781</v>
       </c>
       <c r="R5" t="n">
-        <v>7035412</v>
+        <v>7035475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,22 +1120,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721713</v>
+        <v>122721503</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1224,14 +1194,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519772</v>
+        <v>519795</v>
       </c>
       <c r="R6" t="n">
-        <v>7035431</v>
+        <v>7035472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1238,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre ringhack i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,31 +1249,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1320,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721845</v>
+        <v>122722231</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,27 +1281,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1365,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519759</v>
+        <v>519782</v>
       </c>
       <c r="R7" t="n">
-        <v>7035436</v>
+        <v>7035501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,11 +1355,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721503</v>
+        <v>122721724</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1468,7 +1417,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1477,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519795</v>
+        <v>519765</v>
       </c>
       <c r="R8" t="n">
-        <v>7035472</v>
+        <v>7035442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122721910</v>
+        <v>122721914</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1580,7 +1529,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1589,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519754</v>
+        <v>519756</v>
       </c>
       <c r="R9" t="n">
-        <v>7035420</v>
+        <v>7035416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1625,11 +1574,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721914</v>
+        <v>122722054</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,27 +1616,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1701,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519756</v>
+        <v>519758</v>
       </c>
       <c r="R10" t="n">
-        <v>7035416</v>
+        <v>7035414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,6 +1683,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1747,6 +1696,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1763,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721724</v>
+        <v>122722060</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,43 +1749,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519765</v>
+        <v>519759</v>
       </c>
       <c r="R11" t="n">
-        <v>7035442</v>
+        <v>7035412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,11 +1820,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1859,6 +1828,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1875,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722127</v>
+        <v>122721845</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,34 +1885,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519724</v>
+        <v>519759</v>
       </c>
       <c r="R12" t="n">
-        <v>7035446</v>
+        <v>7035436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,6 +1952,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1961,31 +1965,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2002,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122722231</v>
+        <v>122721713</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,48 +1997,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519782</v>
+        <v>519772</v>
       </c>
       <c r="R13" t="n">
-        <v>7035501</v>
+        <v>7035431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,6 +2064,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2077,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122722127</v>
+        <v>122721845</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519724</v>
+        <v>519759</v>
       </c>
       <c r="R3" t="n">
-        <v>7035446</v>
+        <v>7035436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +870,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721910</v>
+        <v>122722231</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +915,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519754</v>
+        <v>519782</v>
       </c>
       <c r="R4" t="n">
-        <v>7035420</v>
+        <v>7035501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721604</v>
+        <v>122722060</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1027,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519781</v>
+        <v>519759</v>
       </c>
       <c r="R5" t="n">
-        <v>7035475</v>
+        <v>7035412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,22 +1114,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721503</v>
+        <v>122721713</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1194,14 +1188,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519795</v>
+        <v>519772</v>
       </c>
       <c r="R6" t="n">
-        <v>7035472</v>
+        <v>7035431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,6 +1243,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1265,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722231</v>
+        <v>122721910</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,48 +1300,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519782</v>
+        <v>519754</v>
       </c>
       <c r="R7" t="n">
-        <v>7035501</v>
+        <v>7035420</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,6 +1365,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721724</v>
+        <v>122721503</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1417,7 +1432,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519765</v>
+        <v>519795</v>
       </c>
       <c r="R8" t="n">
-        <v>7035442</v>
+        <v>7035472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122721914</v>
+        <v>122721604</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,39 +1524,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519756</v>
+        <v>519781</v>
       </c>
       <c r="R9" t="n">
-        <v>7035416</v>
+        <v>7035475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,6 +1594,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1737,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722060</v>
+        <v>122721724</v>
       </c>
       <c r="B11" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,43 +1784,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519759</v>
+        <v>519765</v>
       </c>
       <c r="R11" t="n">
-        <v>7035412</v>
+        <v>7035442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,6 +1855,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1828,31 +1868,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1869,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721845</v>
+        <v>122722127</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,39 +1900,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519759</v>
+        <v>519724</v>
       </c>
       <c r="R12" t="n">
-        <v>7035436</v>
+        <v>7035446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,11 +1962,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1965,6 +1970,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1981,7 +2011,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721713</v>
+        <v>122721914</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2026,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519772</v>
+        <v>519756</v>
       </c>
       <c r="R13" t="n">
-        <v>7035431</v>
+        <v>7035416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,11 +2094,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2077,31 +2102,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721845</v>
+        <v>122722231</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +803,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519759</v>
+        <v>519782</v>
       </c>
       <c r="R3" t="n">
-        <v>7035436</v>
+        <v>7035501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122722231</v>
+        <v>122721845</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,36 +919,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519782</v>
+        <v>519759</v>
       </c>
       <c r="R4" t="n">
-        <v>7035501</v>
+        <v>7035436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122722231</v>
+        <v>122721845</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,36 +803,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519782</v>
+        <v>519759</v>
       </c>
       <c r="R3" t="n">
-        <v>7035501</v>
+        <v>7035436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721845</v>
+        <v>122722231</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,27 +915,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519759</v>
+        <v>519782</v>
       </c>
       <c r="R4" t="n">
-        <v>7035436</v>
+        <v>7035501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721845</v>
+        <v>122721914</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -823,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519759</v>
+        <v>519756</v>
       </c>
       <c r="R3" t="n">
-        <v>7035436</v>
+        <v>7035416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122722231</v>
+        <v>122721724</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,36 +910,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519782</v>
+        <v>519765</v>
       </c>
       <c r="R4" t="n">
-        <v>7035501</v>
+        <v>7035442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722060</v>
+        <v>122722231</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1018,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519759</v>
+        <v>519782</v>
       </c>
       <c r="R5" t="n">
-        <v>7035412</v>
+        <v>7035501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,31 +1106,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1147,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721713</v>
+        <v>122721604</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1138,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519772</v>
+        <v>519781</v>
       </c>
       <c r="R6" t="n">
-        <v>7035431</v>
+        <v>7035475</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,11 +1200,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1261,12 +1226,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1284,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721910</v>
+        <v>122721503</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1320,19 +1285,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519754</v>
+        <v>519795</v>
       </c>
       <c r="R7" t="n">
-        <v>7035420</v>
+        <v>7035472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721503</v>
+        <v>122721713</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1437,14 +1402,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519795</v>
+        <v>519772</v>
       </c>
       <c r="R8" t="n">
-        <v>7035472</v>
+        <v>7035431</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1446,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1457,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122721604</v>
+        <v>122722127</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1548,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519781</v>
+        <v>519724</v>
       </c>
       <c r="R9" t="n">
-        <v>7035475</v>
+        <v>7035446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122722054</v>
+        <v>122721910</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,27 +1641,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1680,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519758</v>
+        <v>519754</v>
       </c>
       <c r="R10" t="n">
-        <v>7035414</v>
+        <v>7035420</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,31 +1721,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1772,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122721724</v>
+        <v>122722060</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1784,43 +1749,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519765</v>
+        <v>519759</v>
       </c>
       <c r="R11" t="n">
-        <v>7035442</v>
+        <v>7035412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1855,11 +1820,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1868,6 +1828,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1884,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722127</v>
+        <v>122722054</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,34 +1885,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519724</v>
+        <v>519758</v>
       </c>
       <c r="R12" t="n">
-        <v>7035446</v>
+        <v>7035414</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,6 +1952,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1978,22 +1973,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721914</v>
+        <v>122721845</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2047,19 +2042,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519756</v>
+        <v>519759</v>
       </c>
       <c r="R13" t="n">
-        <v>7035416</v>
+        <v>7035436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2092,6 +2087,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721914</v>
+        <v>122721713</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519756</v>
+        <v>519772</v>
       </c>
       <c r="R3" t="n">
-        <v>7035416</v>
+        <v>7035431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721724</v>
+        <v>122721845</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -939,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519765</v>
+        <v>519759</v>
       </c>
       <c r="R4" t="n">
-        <v>7035442</v>
+        <v>7035436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +1009,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722231</v>
+        <v>122722060</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,52 +1048,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519782</v>
+        <v>519759</v>
       </c>
       <c r="R5" t="n">
-        <v>7035501</v>
+        <v>7035412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,6 +1127,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721604</v>
+        <v>122721724</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,34 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519781</v>
+        <v>519765</v>
       </c>
       <c r="R6" t="n">
-        <v>7035475</v>
+        <v>7035442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,6 +1251,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1208,31 +1264,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1249,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122721503</v>
+        <v>122722054</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1296,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519795</v>
+        <v>519758</v>
       </c>
       <c r="R7" t="n">
-        <v>7035472</v>
+        <v>7035414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1365,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,6 +1376,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1361,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721713</v>
+        <v>122721604</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1433,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519772</v>
+        <v>519781</v>
       </c>
       <c r="R8" t="n">
-        <v>7035431</v>
+        <v>7035475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,11 +1495,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1475,12 +1521,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1498,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122722127</v>
+        <v>122722231</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,34 +1560,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519724</v>
+        <v>519782</v>
       </c>
       <c r="R9" t="n">
-        <v>7035446</v>
+        <v>7035501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,31 +1644,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,7 +1660,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721910</v>
+        <v>122721503</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1661,19 +1696,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519754</v>
+        <v>519795</v>
       </c>
       <c r="R10" t="n">
-        <v>7035420</v>
+        <v>7035472</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722060</v>
+        <v>122722127</v>
       </c>
       <c r="B11" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,43 +1784,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519759</v>
+        <v>519724</v>
       </c>
       <c r="R11" t="n">
-        <v>7035412</v>
+        <v>7035446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,22 +1866,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1869,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122722054</v>
+        <v>122721910</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,27 +1915,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1914,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519758</v>
+        <v>519754</v>
       </c>
       <c r="R12" t="n">
-        <v>7035414</v>
+        <v>7035420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1984,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,31 +1995,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2006,7 +2011,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721845</v>
+        <v>122721914</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2042,19 +2047,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519759</v>
+        <v>519756</v>
       </c>
       <c r="R13" t="n">
-        <v>7035436</v>
+        <v>7035416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,11 +2092,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721713</v>
+        <v>122721845</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519772</v>
+        <v>519759</v>
       </c>
       <c r="R3" t="n">
-        <v>7035431</v>
+        <v>7035436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack i stambasen.</t>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721845</v>
+        <v>122721503</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519759</v>
+        <v>519795</v>
       </c>
       <c r="R4" t="n">
-        <v>7035436</v>
+        <v>7035472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +984,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722060</v>
+        <v>122722231</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,43 +1023,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519759</v>
+        <v>519782</v>
       </c>
       <c r="R5" t="n">
-        <v>7035412</v>
+        <v>7035501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,31 +1111,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1168,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721724</v>
+        <v>122721914</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,19 +1163,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519765</v>
+        <v>519756</v>
       </c>
       <c r="R6" t="n">
-        <v>7035442</v>
+        <v>7035416</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,11 +1208,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1237,7 @@
         <v>122722054</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1420,7 +1374,7 @@
         <v>122721604</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1544,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122722231</v>
+        <v>122721724</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,36 +1514,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1598,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519782</v>
+        <v>519765</v>
       </c>
       <c r="R9" t="n">
-        <v>7035501</v>
+        <v>7035442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,6 +1579,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721503</v>
+        <v>122722060</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,43 +1622,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519795</v>
+        <v>519759</v>
       </c>
       <c r="R10" t="n">
-        <v>7035472</v>
+        <v>7035412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,11 +1693,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1756,6 +1701,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1772,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122722127</v>
+        <v>122721910</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,34 +1758,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519724</v>
+        <v>519754</v>
       </c>
       <c r="R11" t="n">
-        <v>7035446</v>
+        <v>7035420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,6 +1825,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1858,31 +1838,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1899,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721910</v>
+        <v>122721713</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,7 +1890,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1944,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519754</v>
+        <v>519772</v>
       </c>
       <c r="R12" t="n">
-        <v>7035420</v>
+        <v>7035431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,7 +1939,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack i stambasen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,6 +1950,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2011,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122721914</v>
+        <v>122722127</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2027,39 +2007,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519756</v>
+        <v>519724</v>
       </c>
       <c r="R13" t="n">
-        <v>7035416</v>
+        <v>7035446</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,6 +2077,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103266237</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519728.851032736</v>
+        <v>519729</v>
       </c>
       <c r="R2" t="n">
-        <v>7035568.252932162</v>
+        <v>7035568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721845</v>
+        <v>122721604</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519759</v>
+        <v>519781</v>
       </c>
       <c r="R3" t="n">
-        <v>7035436</v>
+        <v>7035475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +845,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +853,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,55 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122721503</v>
+        <v>122722127</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519795</v>
+        <v>519724</v>
       </c>
       <c r="R4" t="n">
-        <v>7035472</v>
+        <v>7035446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,11 +967,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,15 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122722231</v>
+        <v>122722054</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,48 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519782</v>
+        <v>519758</v>
       </c>
       <c r="R5" t="n">
-        <v>7035501</v>
+        <v>7035414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,6 +1094,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1111,6 +1107,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1127,43 +1148,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122721914</v>
+        <v>122722060</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519756</v>
+        <v>519759</v>
       </c>
       <c r="R6" t="n">
-        <v>7035416</v>
+        <v>7035412</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,6 +1234,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1234,15 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122722054</v>
+        <v>122721503</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,39 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519758</v>
+        <v>519795</v>
       </c>
       <c r="R7" t="n">
-        <v>7035414</v>
+        <v>7035472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på en rakväxt gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,31 +1366,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1371,15 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122721604</v>
+        <v>122721713</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,34 +1393,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519781</v>
+        <v>519772</v>
       </c>
       <c r="R8" t="n">
-        <v>7035475</v>
+        <v>7035431</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,6 +1460,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i stambasen.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1475,12 +1491,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1501,12 +1517,7 @@
         <v>122721724</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,55 +1621,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122722060</v>
+        <v>122721845</v>
       </c>
       <c r="B10" t="n">
-        <v>79879</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>519759</v>
       </c>
       <c r="R10" t="n">
-        <v>7035412</v>
+        <v>7035436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,6 +1699,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla och färska ringhack. Ca 3 meter från en hänsynssnitslad tall inom en avverkningsanmäld yta…</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1701,31 +1712,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1745,12 +1731,7 @@
         <v>122721910</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,15 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122721713</v>
+        <v>122721914</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519772</v>
+        <v>519756</v>
       </c>
       <c r="R12" t="n">
-        <v>7035431</v>
+        <v>7035416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,11 +1913,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i stambasen.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1950,31 +1921,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1991,15 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122722127</v>
+        <v>122722231</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,34 +1948,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519724</v>
+        <v>519782</v>
       </c>
       <c r="R13" t="n">
-        <v>7035446</v>
+        <v>7035501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,31 +2032,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 30233-2022 artfynd.xlsx
+++ b/artfynd/A 30233-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103266237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721604</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122722127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122722054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122722060</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721503</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1511,6 +1546,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721713</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721724</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721845</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721910</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122721914</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,8 +2105,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122722231</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>